--- a/reports/youtube_analysis_20260904.xlsx
+++ b/reports/youtube_analysis_20260904.xlsx
@@ -779,6 +779,7 @@
       </c>
       <c r="F15" s="10">
         <f>IFERROR(E15/D15*1000,0)</f>
+        <v>0.7576153404</v>
         <v/>
       </c>
       <c r="G15" s="11" t="n">
@@ -786,10 +787,12 @@
       </c>
       <c r="H15" s="12">
         <f>IFERROR(151/D15*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
+        <v>3.944824703</v>
+        <v/>
+      </c>
+      <c r="I15" t="str" s="11">
         <f>IF(D15&lt;=0,"データなし",IF(F15&gt;=0.6,"良好",IF(F15&gt;=0.4,"標準","要改善")))</f>
+        <v>良好</v>
         <v/>
       </c>
     </row>
@@ -815,6 +818,7 @@
       </c>
       <c r="F16" s="10">
         <f>IFERROR(E16/D16*1000,0)</f>
+        <v>1.418439716</v>
         <v/>
       </c>
       <c r="G16" s="11" t="n">
@@ -822,10 +826,12 @@
       </c>
       <c r="H16" s="12">
         <f>IFERROR(19/D16*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="11">
+        <v>8.983451537</v>
+        <v/>
+      </c>
+      <c r="I16" t="str" s="11">
         <f>IF(D16&lt;=0,"データなし",IF(F16&gt;=0.6,"良好",IF(F16&gt;=0.4,"標準","要改善")))</f>
+        <v>良好</v>
         <v/>
       </c>
     </row>
@@ -851,6 +857,7 @@
       </c>
       <c r="F17" s="10">
         <f>IFERROR(E17/D17*1000,0)</f>
+        <v>0.7926442613</v>
         <v/>
       </c>
       <c r="G17" s="11" t="n">
@@ -858,10 +865,12 @@
       </c>
       <c r="H17" s="12">
         <f>IFERROR(22/D17*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="11">
+        <v>3.48763475</v>
+        <v/>
+      </c>
+      <c r="I17" t="str" s="11">
         <f>IF(D17&lt;=0,"データなし",IF(F17&gt;=0.6,"良好",IF(F17&gt;=0.4,"標準","要改善")))</f>
+        <v>良好</v>
         <v/>
       </c>
     </row>
@@ -887,6 +896,7 @@
       </c>
       <c r="F18" s="10">
         <f>IFERROR(E18/D18*1000,0)</f>
+        <v>0.3047851265</v>
         <v/>
       </c>
       <c r="G18" s="11" t="n">
@@ -894,10 +904,12 @@
       </c>
       <c r="H18" s="12">
         <f>IFERROR(8/D18*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="11">
+        <v>2.438281012</v>
+        <v/>
+      </c>
+      <c r="I18" t="str" s="11">
         <f>IF(D18&lt;=0,"データなし",IF(F18&gt;=0.6,"良好",IF(F18&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -923,6 +935,7 @@
       </c>
       <c r="F19" s="10">
         <f>IFERROR(E19/D19*1000,0)</f>
+        <v>0.6626905235</v>
         <v/>
       </c>
       <c r="G19" s="11" t="n">
@@ -930,10 +943,12 @@
       </c>
       <c r="H19" s="12">
         <f>IFERROR(5/D19*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="11">
+        <v>3.313452618</v>
+        <v/>
+      </c>
+      <c r="I19" t="str" s="11">
         <f>IF(D19&lt;=0,"データなし",IF(F19&gt;=0.6,"良好",IF(F19&gt;=0.4,"標準","要改善")))</f>
+        <v>良好</v>
         <v/>
       </c>
     </row>
@@ -959,6 +974,7 @@
       </c>
       <c r="F20" s="10">
         <f>IFERROR(E20/D20*1000,0)</f>
+        <v>0.2962962963</v>
         <v/>
       </c>
       <c r="G20" s="11" t="n">
@@ -966,10 +982,12 @@
       </c>
       <c r="H20" s="12">
         <f>IFERROR(10/D20*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="11">
+        <v>2.962962963</v>
+        <v/>
+      </c>
+      <c r="I20" t="str" s="11">
         <f>IF(D20&lt;=0,"データなし",IF(F20&gt;=0.6,"良好",IF(F20&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -995,6 +1013,7 @@
       </c>
       <c r="F21" s="10">
         <f>IFERROR(E21/D21*1000,0)</f>
+        <v>0.8335648791</v>
         <v/>
       </c>
       <c r="G21" s="11" t="n">
@@ -1002,10 +1021,12 @@
       </c>
       <c r="H21" s="12">
         <f>IFERROR(7/D21*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="11">
+        <v>1.944984718</v>
+        <v/>
+      </c>
+      <c r="I21" t="str" s="11">
         <f>IF(D21&lt;=0,"データなし",IF(F21&gt;=0.6,"良好",IF(F21&gt;=0.4,"標準","要改善")))</f>
+        <v>良好</v>
         <v/>
       </c>
     </row>
@@ -1031,6 +1052,7 @@
       </c>
       <c r="F22" s="10">
         <f>IFERROR(E22/D22*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="G22" s="11" t="n">
@@ -1038,10 +1060,12 @@
       </c>
       <c r="H22" s="12">
         <f>IFERROR(1/D22*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="11">
+        <v>4.62962963</v>
+        <v/>
+      </c>
+      <c r="I22" t="str" s="11">
         <f>IF(D22&lt;=0,"データなし",IF(F22&gt;=0.6,"良好",IF(F22&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -1067,6 +1091,7 @@
       </c>
       <c r="F23" s="10">
         <f>IFERROR(E23/D23*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="G23" s="11" t="n">
@@ -1074,10 +1099,12 @@
       </c>
       <c r="H23" s="12">
         <f>IFERROR(54/D23*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="11">
+        <v>1.862390067</v>
+        <v/>
+      </c>
+      <c r="I23" t="str" s="11">
         <f>IF(D23&lt;=0,"データなし",IF(F23&gt;=0.6,"良好",IF(F23&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -1103,6 +1130,7 @@
       </c>
       <c r="F24" s="10">
         <f>IFERROR(E24/D24*1000,0)</f>
+        <v>0.1902135147</v>
         <v/>
       </c>
       <c r="G24" s="11" t="n">
@@ -1110,10 +1138,12 @@
       </c>
       <c r="H24" s="12">
         <f>IFERROR(51/D24*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="11">
+        <v>2.425222312</v>
+        <v/>
+      </c>
+      <c r="I24" t="str" s="11">
         <f>IF(D24&lt;=0,"データなし",IF(F24&gt;=0.6,"良好",IF(F24&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -1139,6 +1169,7 @@
       </c>
       <c r="F25" s="10">
         <f>IFERROR(E25/D25*1000,0)</f>
+        <v>0.1652710445</v>
         <v/>
       </c>
       <c r="G25" s="11" t="n">
@@ -1146,10 +1177,12 @@
       </c>
       <c r="H25" s="12">
         <f>IFERROR(48/D25*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="11">
+        <v>2.644336712</v>
+        <v/>
+      </c>
+      <c r="I25" t="str" s="11">
         <f>IF(D25&lt;=0,"データなし",IF(F25&gt;=0.6,"良好",IF(F25&gt;=0.4,"標準","要改善")))</f>
+        <v>要改善</v>
         <v/>
       </c>
     </row>
@@ -1175,6 +1208,7 @@
       </c>
       <c r="F26" s="10">
         <f>IFERROR(E26/D26*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="G26" s="11" t="n">
@@ -1182,10 +1216,12 @@
       </c>
       <c r="H26" s="12">
         <f>IFERROR(0/D26*1000,0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="11">
+        <v>0</v>
+        <v/>
+      </c>
+      <c r="I26" t="str" s="11">
         <f>IF(D26&lt;=0,"データなし",IF(F26&gt;=0.6,"良好",IF(F26&gt;=0.4,"標準","要改善")))</f>
+        <v>データなし</v>
         <v/>
       </c>
     </row>
@@ -1198,18 +1234,22 @@
       <c r="B27" s="7" t="inlineStr"/>
       <c r="C27" s="13">
         <f>SUM(C15:C26)</f>
+        <v>296</v>
         <v/>
       </c>
       <c r="D27" s="14">
         <f>SUM(D15:D26)</f>
+        <v>126857</v>
         <v/>
       </c>
       <c r="E27" s="13">
         <f>SUM(E15:E26)</f>
+        <v>50</v>
         <v/>
       </c>
       <c r="F27" s="15">
         <f>IFERROR(E27/D27*1000,0)</f>
+        <v>0.394144588</v>
         <v/>
       </c>
     </row>
@@ -2010,6 +2050,7 @@
       </c>
       <c r="G5" s="10">
         <f>IFERROR(E5/D5*1000,0)</f>
+        <v>0.192566917</v>
         <v/>
       </c>
       <c r="H5" s="11" t="n">
@@ -2049,6 +2090,7 @@
       </c>
       <c r="G6" s="10">
         <f>IFERROR(E6/D6*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H6" s="11" t="n">
@@ -2088,6 +2130,7 @@
       </c>
       <c r="G7" s="10">
         <f>IFERROR(E7/D7*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H7" s="11" t="n">
@@ -2127,6 +2170,7 @@
       </c>
       <c r="G8" s="10">
         <f>IFERROR(E8/D8*1000,0)</f>
+        <v>0.7690828687</v>
         <v/>
       </c>
       <c r="H8" s="11" t="n">
@@ -2166,6 +2210,7 @@
       </c>
       <c r="G9" s="10">
         <f>IFERROR(E9/D9*1000,0)</f>
+        <v>0.1993223042</v>
         <v/>
       </c>
       <c r="H9" s="11" t="n">
@@ -2205,6 +2250,7 @@
       </c>
       <c r="G10" s="10">
         <f>IFERROR(E10/D10*1000,0)</f>
+        <v>1.668056714</v>
         <v/>
       </c>
       <c r="H10" s="11" t="n">
@@ -2244,6 +2290,7 @@
       </c>
       <c r="G11" s="10">
         <f>IFERROR(E11/D11*1000,0)</f>
+        <v>1.339883877</v>
         <v/>
       </c>
       <c r="H11" s="11" t="n">
@@ -2283,6 +2330,7 @@
       </c>
       <c r="G12" s="10">
         <f>IFERROR(E12/D12*1000,0)</f>
+        <v>1.015228426</v>
         <v/>
       </c>
       <c r="H12" s="11" t="n">
@@ -2322,6 +2370,7 @@
       </c>
       <c r="G13" s="10">
         <f>IFERROR(E13/D13*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H13" s="11" t="n">
@@ -2361,6 +2410,7 @@
       </c>
       <c r="G14" s="10">
         <f>IFERROR(E14/D14*1000,0)</f>
+        <v>0.5970149254</v>
         <v/>
       </c>
       <c r="H14" s="11" t="n">
@@ -2400,6 +2450,7 @@
       </c>
       <c r="G15" s="10">
         <f>IFERROR(E15/D15*1000,0)</f>
+        <v>0.600240096</v>
         <v/>
       </c>
       <c r="H15" s="11" t="n">
@@ -2439,6 +2490,7 @@
       </c>
       <c r="G16" s="10">
         <f>IFERROR(E16/D16*1000,0)</f>
+        <v>0.6756756757</v>
         <v/>
       </c>
       <c r="H16" s="11" t="n">
@@ -2478,6 +2530,7 @@
       </c>
       <c r="G17" s="10">
         <f>IFERROR(E17/D17*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H17" s="11" t="n">
@@ -2517,6 +2570,7 @@
       </c>
       <c r="G18" s="10">
         <f>IFERROR(E18/D18*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H18" s="11" t="n">
@@ -2556,6 +2610,7 @@
       </c>
       <c r="G19" s="10">
         <f>IFERROR(E19/D19*1000,0)</f>
+        <v>0.7479431563</v>
         <v/>
       </c>
       <c r="H19" s="11" t="n">
@@ -2595,6 +2650,7 @@
       </c>
       <c r="G20" s="10">
         <f>IFERROR(E20/D20*1000,0)</f>
+        <v>0.7518796992</v>
         <v/>
       </c>
       <c r="H20" s="11" t="n">
@@ -2634,6 +2690,7 @@
       </c>
       <c r="G21" s="10">
         <f>IFERROR(E21/D21*1000,0)</f>
+        <v>0.7552870091</v>
         <v/>
       </c>
       <c r="H21" s="11" t="n">
@@ -2673,6 +2730,7 @@
       </c>
       <c r="G22" s="10">
         <f>IFERROR(E22/D22*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H22" s="11" t="n">
@@ -2712,6 +2770,7 @@
       </c>
       <c r="G23" s="10">
         <f>IFERROR(E23/D23*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H23" s="11" t="n">
@@ -2751,6 +2810,7 @@
       </c>
       <c r="G24" s="10">
         <f>IFERROR(E24/D24*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H24" s="11" t="n">
@@ -2790,6 +2850,7 @@
       </c>
       <c r="G25" s="10">
         <f>IFERROR(E25/D25*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H25" s="11" t="n">
@@ -2829,6 +2890,7 @@
       </c>
       <c r="G26" s="10">
         <f>IFERROR(E26/D26*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H26" s="11" t="n">
@@ -2868,6 +2930,7 @@
       </c>
       <c r="G27" s="10">
         <f>IFERROR(E27/D27*1000,0)</f>
+        <v>0.8250825083</v>
         <v/>
       </c>
       <c r="H27" s="11" t="n">
@@ -2907,6 +2970,7 @@
       </c>
       <c r="G28" s="10">
         <f>IFERROR(E28/D28*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H28" s="11" t="n">
@@ -2946,6 +3010,7 @@
       </c>
       <c r="G29" s="10">
         <f>IFERROR(E29/D29*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H29" s="11" t="n">
@@ -2985,6 +3050,7 @@
       </c>
       <c r="G30" s="10">
         <f>IFERROR(E30/D30*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H30" s="11" t="n">
@@ -3024,6 +3090,7 @@
       </c>
       <c r="G31" s="10">
         <f>IFERROR(E31/D31*1000,0)</f>
+        <v>0.837520938</v>
         <v/>
       </c>
       <c r="H31" s="11" t="n">
@@ -3063,6 +3130,7 @@
       </c>
       <c r="G32" s="10">
         <f>IFERROR(E32/D32*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H32" s="11" t="n">
@@ -3102,6 +3170,7 @@
       </c>
       <c r="G33" s="10">
         <f>IFERROR(E33/D33*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H33" s="11" t="n">
@@ -3141,6 +3210,7 @@
       </c>
       <c r="G34" s="10">
         <f>IFERROR(E34/D34*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H34" s="11" t="n">
@@ -3180,6 +3250,7 @@
       </c>
       <c r="G35" s="10">
         <f>IFERROR(E35/D35*1000,0)</f>
+        <v>1.706484642</v>
         <v/>
       </c>
       <c r="H35" s="11" t="n">
@@ -3219,6 +3290,7 @@
       </c>
       <c r="G36" s="10">
         <f>IFERROR(E36/D36*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H36" s="11" t="n">
@@ -3258,6 +3330,7 @@
       </c>
       <c r="G37" s="10">
         <f>IFERROR(E37/D37*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H37" s="11" t="n">
@@ -3297,6 +3370,7 @@
       </c>
       <c r="G38" s="10">
         <f>IFERROR(E38/D38*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H38" s="11" t="n">
@@ -3336,6 +3410,7 @@
       </c>
       <c r="G39" s="10">
         <f>IFERROR(E39/D39*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H39" s="11" t="n">
@@ -3375,6 +3450,7 @@
       </c>
       <c r="G40" s="10">
         <f>IFERROR(E40/D40*1000,0)</f>
+        <v>1.78412132</v>
         <v/>
       </c>
       <c r="H40" s="11" t="n">
@@ -3414,6 +3490,7 @@
       </c>
       <c r="G41" s="10">
         <f>IFERROR(E41/D41*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H41" s="11" t="n">
@@ -3453,6 +3530,7 @@
       </c>
       <c r="G42" s="10">
         <f>IFERROR(E42/D42*1000,0)</f>
+        <v>0.9191176471</v>
         <v/>
       </c>
       <c r="H42" s="11" t="n">
@@ -3492,6 +3570,7 @@
       </c>
       <c r="G43" s="10">
         <f>IFERROR(E43/D43*1000,0)</f>
+        <v>0.9199632015</v>
         <v/>
       </c>
       <c r="H43" s="11" t="n">
@@ -3531,6 +3610,7 @@
       </c>
       <c r="G44" s="10">
         <f>IFERROR(E44/D44*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H44" s="11" t="n">
@@ -3570,6 +3650,7 @@
       </c>
       <c r="G45" s="10">
         <f>IFERROR(E45/D45*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H45" s="11" t="n">
@@ -3609,6 +3690,7 @@
       </c>
       <c r="G46" s="10">
         <f>IFERROR(E46/D46*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H46" s="11" t="n">
@@ -3648,6 +3730,7 @@
       </c>
       <c r="G47" s="10">
         <f>IFERROR(E47/D47*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H47" s="11" t="n">
@@ -3687,6 +3770,7 @@
       </c>
       <c r="G48" s="10">
         <f>IFERROR(E48/D48*1000,0)</f>
+        <v>1.892147588</v>
         <v/>
       </c>
       <c r="H48" s="11" t="n">
@@ -3726,6 +3810,7 @@
       </c>
       <c r="G49" s="10">
         <f>IFERROR(E49/D49*1000,0)</f>
+        <v>0.946969697</v>
         <v/>
       </c>
       <c r="H49" s="11" t="n">
@@ -3765,6 +3850,7 @@
       </c>
       <c r="G50" s="10">
         <f>IFERROR(E50/D50*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H50" s="11" t="n">
@@ -3804,6 +3890,7 @@
       </c>
       <c r="G51" s="10">
         <f>IFERROR(E51/D51*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H51" s="11" t="n">
@@ -3843,6 +3930,7 @@
       </c>
       <c r="G52" s="10">
         <f>IFERROR(E52/D52*1000,0)</f>
+        <v>0.9671179884</v>
         <v/>
       </c>
       <c r="H52" s="11" t="n">
@@ -3882,6 +3970,7 @@
       </c>
       <c r="G53" s="10">
         <f>IFERROR(E53/D53*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H53" s="11" t="n">
@@ -3921,6 +4010,7 @@
       </c>
       <c r="G54" s="10">
         <f>IFERROR(E54/D54*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H54" s="11" t="n">
@@ -3960,6 +4050,7 @@
       </c>
       <c r="G55" s="10">
         <f>IFERROR(E55/D55*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H55" s="11" t="n">
@@ -3999,6 +4090,7 @@
       </c>
       <c r="G56" s="10">
         <f>IFERROR(E56/D56*1000,0)</f>
+        <v>1.007049345</v>
         <v/>
       </c>
       <c r="H56" s="11" t="n">
@@ -4038,6 +4130,7 @@
       </c>
       <c r="G57" s="10">
         <f>IFERROR(E57/D57*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H57" s="11" t="n">
@@ -4077,6 +4170,7 @@
       </c>
       <c r="G58" s="10">
         <f>IFERROR(E58/D58*1000,0)</f>
+        <v>2.028397566</v>
         <v/>
       </c>
       <c r="H58" s="11" t="n">
@@ -4116,6 +4210,7 @@
       </c>
       <c r="G59" s="10">
         <f>IFERROR(E59/D59*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H59" s="11" t="n">
@@ -4155,6 +4250,7 @@
       </c>
       <c r="G60" s="10">
         <f>IFERROR(E60/D60*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H60" s="11" t="n">
@@ -4194,6 +4290,7 @@
       </c>
       <c r="G61" s="10">
         <f>IFERROR(E61/D61*1000,0)</f>
+        <v>0</v>
         <v/>
       </c>
       <c r="H61" s="11" t="n">
@@ -4233,6 +4330,7 @@
       </c>
       <c r="G62" s="10">
         <f>IFERROR(E62/D62*1000,0)</f>
+        <v>2.085505735</v>
         <v/>
       </c>
       <c r="H62" s="11" t="n">
@@ -4272,6 +4370,7 @@
       </c>
       <c r="G63" s="10">
         <f>IFERROR(E63/D63*1000,0)</f>
+        <v>1.049317943</v>
         <v/>
       </c>
       <c r="H63" s="11" t="n">
@@ -4311,6 +4410,7 @@
       </c>
       <c r="G64" s="10">
         <f>IFERROR(E64/D64*1000,0)</f>
+        <v>2.116402116</v>
         <v/>
       </c>
       <c r="H64" s="11" t="n">
@@ -4770,6 +4870,7 @@
       </c>
       <c r="F5" s="21">
         <f>IFERROR(B5/D5,0)</f>
+        <v>1.5</v>
         <v/>
       </c>
       <c r="G5" s="7" t="n">
@@ -4806,6 +4907,7 @@
       </c>
       <c r="F6" s="21">
         <f>IFERROR(B6/D6,0)</f>
+        <v>1.666666667</v>
         <v/>
       </c>
       <c r="G6" s="7" t="n">
@@ -4842,6 +4944,7 @@
       </c>
       <c r="F7" s="21">
         <f>IFERROR(B7/D7,0)</f>
+        <v>0.74</v>
         <v/>
       </c>
       <c r="G7" s="7" t="n">
@@ -4878,6 +4981,7 @@
       </c>
       <c r="F8" s="21">
         <f>IFERROR(B8/D8,0)</f>
+        <v>1.25</v>
         <v/>
       </c>
       <c r="G8" s="7" t="n">
@@ -4914,6 +5018,7 @@
       </c>
       <c r="F9" s="21">
         <f>IFERROR(B9/D9,0)</f>
+        <v>1.5</v>
         <v/>
       </c>
       <c r="G9" s="7" t="n">
